--- a/results/Int Task Remove ACC -0.6/Rando_4_permute.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_4_permute.xlsx
@@ -440,517 +440,517 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7185648582047628</v>
+        <v>0.7215195969241157</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7087152621632337</v>
+        <v>0.7199531808840155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7155152064061775</v>
+        <v>0.7199531808840155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7230769069123339</v>
+        <v>0.7212063137160958</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7230431094505407</v>
+        <v>0.7220447709547766</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7224841379580869</v>
+        <v>0.7083005865698344</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7224841379580869</v>
+        <v>0.7159701587675169</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7133560214118303</v>
+        <v>0.7098799612222283</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7128308473811695</v>
+        <v>0.7098799612222283</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7140995655712786</v>
+        <v>0.708000261974108</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7162249531038328</v>
+        <v>0.7037923904226749</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7175885843731744</v>
+        <v>0.714538932574589</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7305683857491689</v>
+        <v>0.7208045967349901</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7125396288373254</v>
+        <v>0.7273094698736781</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.710659929589205</v>
+        <v>0.729481613480319</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7276071677236692</v>
+        <v>0.7292021277340921</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7215260762302627</v>
+        <v>0.7274667243850264</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7232432674755642</v>
+        <v>0.7281491529270353</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7232432674755642</v>
+        <v>0.7198230694119312</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7269103796383076</v>
+        <v>0.7267244060402543</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7143426271099773</v>
+        <v>0.7120871281053388</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7012094237830462</v>
+        <v>0.7156516220680265</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7066639488604126</v>
+        <v>0.6978230231812063</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7139552696722242</v>
+        <v>0.6978230231812063</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6841348760386152</v>
+        <v>0.6969845659425254</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7000694161339627</v>
+        <v>0.6915170822528653</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6944030002339555</v>
+        <v>0.6915664650726874</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6980336881891706</v>
+        <v>0.6803661963741102</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7043604679670109</v>
+        <v>0.6795056744712535</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7171465906241288</v>
+        <v>0.6707766481603674</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7165785130797928</v>
+        <v>0.6562330574900079</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7165785130797928</v>
+        <v>0.6513310245989485</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7187103799184938</v>
+        <v>0.6555726936121746</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.718126717016129</v>
+        <v>0.6556064910739678</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7182034179915973</v>
+        <v>0.6437446326828811</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7182034179915973</v>
+        <v>0.6437784301446741</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6967506104557089</v>
+        <v>0.6126035112936057</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6825097960104285</v>
+        <v>0.6295637080403635</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6848717657755343</v>
+        <v>0.6381640238102242</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6857440204760084</v>
+        <v>0.6390024810489051</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6662463873490321</v>
+        <v>0.640154221495606</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6764871933887262</v>
+        <v>0.642212014104574</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6574159686527666</v>
+        <v>0.6515247033178251</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6478237936932886</v>
+        <v>0.6607789036593721</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6448898938234351</v>
+        <v>0.6281741595464345</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6448898938234351</v>
+        <v>0.6028969853364545</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6124917870416678</v>
+        <v>0.5754452158904808</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6071827836780324</v>
+        <v>0.5810893920099298</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5853140747340683</v>
+        <v>0.5975062026222627</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5581428417326155</v>
+        <v>0.5978194858302828</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5624950091831031</v>
+        <v>0.5975062026222627</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5353134443150919</v>
+        <v>0.5974541930567054</v>
       </c>
     </row>
     <row r="54">
@@ -960,327 +960,327 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5353134443150919</v>
+        <v>0.5974541930567054</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5328695200830472</v>
+        <v>0.5881441305891896</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5148707080725851</v>
+        <v>0.5801001595660475</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5272798051585084</v>
+        <v>0.5758584905528215</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5219228199061096</v>
+        <v>0.5843183629840392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5219228199061096</v>
+        <v>0.5959098416807811</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5164696957598019</v>
+        <v>0.6031088761590954</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5253794421772711</v>
+        <v>0.5589138791640924</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5253794421772711</v>
+        <v>0.555781047083892</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5260996958578671</v>
+        <v>0.5621454768839371</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5301203679965705</v>
+        <v>0.5607310618637147</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5435341077680227</v>
+        <v>0.5732103806189593</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5178813089179068</v>
+        <v>0.5455544254711682</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5138254383863516</v>
+        <v>0.535031506939512</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4998719899245038</v>
+        <v>0.5750641626424922</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4717491745013737</v>
+        <v>0.5691650170703449</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4841635250787674</v>
+        <v>0.5663701596080756</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4882453128349101</v>
+        <v>0.568004170571762</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5270743936420145</v>
+        <v>0.551075144541062</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6061632561000041</v>
+        <v>0.5528105478901277</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5798500933720551</v>
+        <v>0.5254768068858563</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5732114313172534</v>
+        <v>0.5238245838184057</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5757138444210022</v>
+        <v>0.5494723042934334</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5399801207882758</v>
+        <v>0.5384333177829986</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5545862280071335</v>
+        <v>0.5151034377447251</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5532031588193513</v>
+        <v>0.5151034377447251</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5139322593795836</v>
+        <v>0.5208166097188192</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5277904445294342</v>
+        <v>0.5261072258623081</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5369068282780736</v>
+        <v>0.526386711608535</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5291267576431297</v>
+        <v>0.526386711608535</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5227894708823484</v>
+        <v>0.5387488775039891</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5227894708823484</v>
+        <v>0.517047930054314</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5058853113779418</v>
+        <v>0.506330106989105</v>
       </c>
     </row>
     <row r="87">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4960353651036479</v>
+        <v>0.5267204834332898</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4960353651036479</v>
+        <v>0.5255323187790606</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4950708240696767</v>
+        <v>0.4926559691571019</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4950708240696767</v>
+        <v>0.4977644642629492</v>
       </c>
     </row>
   </sheetData>
